--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_lstm_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_lstm_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>0.9516577557503278</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,35 +1041,35 @@
         <v>0.8699837092823588</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.4325158389774142</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,75 +1343,75 @@
         <v>0.8924631237587328</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>0.9516577557503278</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,75 +1663,75 @@
         <v>0.9516577557503278</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -1829,51 +1830,51 @@
         <v>0.7591528709001734</v>
       </c>
       <c r="AD9" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AI9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH9" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,43 +1983,43 @@
         <v>0.8924631237587328</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
@@ -2026,31 +2027,31 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>39276</v>
+        <v>36105</v>
       </c>
       <c r="M3" t="n">
-        <v>1835</v>
+        <v>79</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="P3" t="n">
-        <v>1827</v>
+        <v>77</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.2522832883059996</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.2481939300735364</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1197</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.9293424274898392</v>
+        <v>0.2116308787151915</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M4" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P4" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.142833728067601</v>
+        <v>-0.002912456372281845</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1849527597465191</v>
+        <v>0.01170303256616578</v>
       </c>
       <c r="AH4" t="n">
-        <v>-805</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>39035</v>
+        <v>36105</v>
       </c>
       <c r="M5" t="n">
-        <v>1671</v>
+        <v>79</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1749267455229749</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1843606641792332</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="P5" t="n">
-        <v>1663</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1345350586651795</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1263048256104209</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1749267455229749</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1843606641792332</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.212013593427959</v>
+        <v>0.2116308787151915</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1218891044631155</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3067619450113204</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>39192</v>
+        <v>36105</v>
       </c>
       <c r="M6" t="n">
-        <v>1777</v>
+        <v>79</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4235499890422761</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4301411401713009</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="P6" t="n">
-        <v>1769</v>
+        <v>77</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2122049733693596</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2054413077636977</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4235499890422761</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4301411401713009</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1194</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.7347558001405585</v>
+        <v>0.2116308787151915</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04275262230983873</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.05813870149201916</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.1000811057577622</v>
+        <v>0.002912456372281845</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.1268140582545</v>
+        <v>-0.01170303256616578</v>
       </c>
       <c r="AL6" t="n">
-        <v>802</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,34 +2963,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>39276</v>
+        <v>36105</v>
       </c>
       <c r="M7" t="n">
-        <v>1835</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="P7" t="n">
-        <v>1827</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.2522832883059996</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2481939300735364</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -2989,29 +3000,31 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1197</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.9293424274898392</v>
+        <v>0.2116308787151915</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -3079,34 +3092,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>39276</v>
+        <v>36105</v>
       </c>
       <c r="M8" t="n">
-        <v>1835</v>
+        <v>79</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="P8" t="n">
-        <v>1827</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2522832883059996</v>
+        <v>0.09666256119913624</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2481939300735364</v>
+        <v>0.04183977632490837</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -3116,29 +3129,31 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4816886905342953</v>
+        <v>-0.1746661317674605</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4876150815614987</v>
+        <v>-0.1807089992694972</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1197</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.9293424274898392</v>
+        <v>0.2116308787151915</v>
       </c>
       <c r="AF8" s="3" t="n">
         <v>0</v>
@@ -3153,13 +3168,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.142833728067601</v>
+        <v>0.002912456372281845</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.1849527597465191</v>
+        <v>-0.01170303256616578</v>
       </c>
       <c r="AL8" t="n">
-        <v>805</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -3210,83 +3225,87 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>37538</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4249696522996184</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4315445709455075</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1889</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2564176052891206</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2564176052891206</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.05869531246089255</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>638</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4249696522996184</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4315445709455075</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1258</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.7390386507410003</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.008223675215584147</v>
+        <v>-0.04183977632490837</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.05671903823467694</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.1746661317674605</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-48</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.2831317115626313</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.1996010640335363</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3335,34 +3354,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>39356</v>
+        <v>36105</v>
       </c>
       <c r="M10" t="n">
-        <v>1890</v>
+        <v>79</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.4577579154268409</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.4639579318376328</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P10" t="n">
-        <v>1882</v>
+        <v>78</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.2448513567137217</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.2444638312426022</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -3372,56 +3391,62 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4577579154268409</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4639579318376328</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1252</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.8441947396745821</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.00373009883093417</v>
+        <v>-0.002912456372281845</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.02393077510745445</v>
+        <v>0.01170303256616578</v>
       </c>
       <c r="AH10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1391036292366668</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.1610219846390647</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>860</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.2831317115626313</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.02133210379490591</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3718,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3827,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>39276</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1834</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.480465778751608</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1823</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2523520150009724</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.2482593675457558</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40967</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1105</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4706028507084904</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4718154607749649</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1103</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1883773997556111</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1192698055249621</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3864,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4706028507084904</v>
+        <v>-0.480465778751608</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4718154607749649</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>750</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-110</v>
-      </c>
+        <v>1197</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.8889410366835118</v>
+        <v>0.9248010219559624</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3944,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M4" t="n">
+        <v>974</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P4" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40956</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1099</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1098</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2062376999383152</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1302232557034226</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3981,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>744</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-116</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.01095345017846046</v>
+        <v>-0.1428715725228941</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.005366867654803209</v>
+        <v>0.1853165108120071</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6</v>
+        <v>-805</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4069,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>39016</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1657</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1729800548256017</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.184360664179233</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1646</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1350898496571025</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1263268930364991</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41338</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1359</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.07966263072905788</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.08177070849265045</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1357</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.04487238774917922</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.03150451395276935</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4106,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>-322</v>
+        <v>-449</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.07966263072905788</v>
+        <v>-0.1729800548256017</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.08177070849265045</v>
+        <v>-0.184360664179233</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1326</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>466</v>
-      </c>
+        <v>1469</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.08655807466794885</v>
+        <v>0.2091606808698241</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08776529157219277</v>
+        <v>-0.1219324745092567</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3909402199794325</v>
+        <v>0.3074857239260063</v>
       </c>
       <c r="AH5" t="n">
-        <v>576</v>
+        <v>272</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4198,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>39192</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1776</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.4221899039010564</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.4301411401713008</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.2122646663982716</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.2054954710716235</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40967</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1105</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4703749864436488</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4715881184443683</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1103</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.2134081641299182</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1351178552535275</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4235,52 +4252,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4703749864436488</v>
+        <v>-0.4221899039010564</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4301411401713008</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>750</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-110</v>
-      </c>
+        <v>1194</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8881283444019241</v>
+        <v>0.7306724246451397</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.01584804972856534</v>
+        <v>-0.04276389647413228</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.0002278642648415596</v>
+        <v>0.05827587485055163</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.004894599550104878</v>
+        <v>0.1001076760487618</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.005139003389961649</v>
+        <v>-0.1270406359614554</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>802</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -4331,34 +4346,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>39276</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1834</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.480465778751608</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1823</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.2523520150009724</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.2482593675457558</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40009</v>
-      </c>
-      <c r="M7" t="n">
-        <v>444</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2576247897817361</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2593252365148109</v>
-      </c>
-      <c r="P7" t="n">
-        <v>442</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.07402588645314596</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.02972951141915425</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -4368,40 +4383,38 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2576247897817361</v>
+        <v>-0.480465778751608</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2593252365148109</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>89</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-771</v>
-      </c>
+        <v>1197</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3470277377742617</v>
+        <v>0.9248010219559624</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.08954029410580788</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2129780609267543</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-661</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4460,34 +4473,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>39276</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1834</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.480465778751608</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.4876150815614988</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1823</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2523520150009724</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2482593675457558</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40592</v>
-      </c>
-      <c r="M8" t="n">
-        <v>848</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.4640066041578759</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.465234323249737</v>
-      </c>
-      <c r="P8" t="n">
-        <v>846</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2041127217184315</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1132264963109398</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4497,52 +4510,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4640066041578759</v>
+        <v>-0.480465778751608</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.465234323249737</v>
+        <v>-0.4876150815614988</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>493</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-367</v>
-      </c>
+        <v>1197</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.8656946293691801</v>
+        <v>0.9248010219559624</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.006043309214022283</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.006596246550614526</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-257</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.01699675939248274</v>
+        <v>0.1428715725228941</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0.001229378895811317</v>
+        <v>-0.1853165108120071</v>
       </c>
       <c r="AL8" t="n">
-        <v>-251</v>
+        <v>805</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -4593,80 +4604,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4236129167340171</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4315445709455076</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.256485211354939</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.256485211354939</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>40361</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40528</v>
-      </c>
-      <c r="M9" t="n">
-        <v>804</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1491889703005721</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1552830514660811</v>
-      </c>
-      <c r="P9" t="n">
-        <v>799</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.05818322981533047</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.03142822948806477</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.05647438350860534</v>
+      </c>
       <c r="W9" t="n">
-        <v>688</v>
+        <v>637</v>
       </c>
       <c r="X9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1491889703005721</v>
+        <v>-0.4236129167340171</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1552830514660811</v>
+        <v>-0.4315445709455076</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>116</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-744</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1753491258255986</v>
+        <v>0.7349451940069487</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.08784157603689735</v>
+        <v>0.008225843809183231</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3214138804079183</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-634</v>
-      </c>
+        <v>0.05685286201759088</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4722,34 +4729,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>39356</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1889</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.456478541000346</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.4639579318376328</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1878</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.244916117654152</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.2445282850788358</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4703749864436488</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4715881184443683</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2116830145154624</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1405325571373974</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4759,52 +4766,50 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>637</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4703749864436488</v>
+        <v>-0.456478541000346</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4715881184443683</v>
+        <v>-0.4639579318376328</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>1252</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.8398537600345908</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.003731082466919944</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.02398723775126199</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>0.1391404900559742</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>-0.1613292730607451</v>
+      </c>
+      <c r="AL10" t="n">
         <v>860</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.8881283444019241</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.02126275161243531</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.0002278642648415596</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01030930143397485</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.005139003389961649</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>116</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -5107,34 +5112,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5144,22 +5149,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5168,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5216,34 +5221,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43537</v>
+        <v>40967</v>
       </c>
       <c r="M3" t="n">
-        <v>117</v>
+        <v>1105</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="P3" t="n">
-        <v>114</v>
+        <v>1103</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.05755410775870121</v>
+        <v>0.1883773997556111</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.03322887960745487</v>
+        <v>0.1192914260826535</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5253,31 +5258,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4706028507084904</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4718154607749649</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>53</v>
+        <v>750</v>
       </c>
       <c r="AC3" t="n">
-        <v>-23</v>
+        <v>-110</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.8889410366835118</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5333,34 +5338,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43559</v>
+        <v>40956</v>
       </c>
       <c r="M4" t="n">
-        <v>133</v>
+        <v>1099</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>1098</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.1302468618407874</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5370,40 +5375,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7</v>
+        <v>-116</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.8699837092823584</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.003475256392701687</v>
+        <v>0.01095543575813387</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01713227410894169</v>
+        <v>0.005366867654803209</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>-6</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5458,34 +5463,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43537</v>
+        <v>41338</v>
       </c>
       <c r="M5" t="n">
-        <v>117</v>
+        <v>1359</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1635746138652394</v>
+        <v>-0.07966263072905788</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1652260547018464</v>
+        <v>-0.08177070849265045</v>
       </c>
       <c r="P5" t="n">
-        <v>114</v>
+        <v>1357</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05755410775870133</v>
+        <v>0.04487238774917922</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03322887960745494</v>
+        <v>0.03151022491338052</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5495,40 +5500,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1635746138652394</v>
+        <v>-0.07966263072905788</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1652260547018464</v>
+        <v>-0.08177070849265045</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>53</v>
+        <v>1326</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23</v>
+        <v>466</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1955639039378525</v>
+        <v>0.08655807466794885</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>6.938893903907228e-17</v>
+        <v>-0.08778120116927302</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0.3909402199794325</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5587,34 +5592,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43537</v>
+        <v>40967</v>
       </c>
       <c r="M6" t="n">
-        <v>117</v>
+        <v>1105</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436488</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
+        <v>1103</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.05755410775870121</v>
+        <v>0.2134081641299182</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.03322887960745487</v>
+        <v>0.1351423486562943</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5624,37 +5629,37 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436488</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>53</v>
+        <v>750</v>
       </c>
       <c r="AC6" t="n">
-        <v>-23</v>
+        <v>-110</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.8881283444019241</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>0.01585092257364082</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.0002278642648415596</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -5663,13 +5668,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.003475256392701687</v>
+        <v>0.004895486815506944</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.01713227410894169</v>
+        <v>-0.005139003389961649</v>
       </c>
       <c r="AL6" t="n">
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -5720,76 +5725,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>40009</v>
+      </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>444</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.2576247897817361</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.2593252365148109</v>
       </c>
       <c r="P7" t="n">
-        <v>351</v>
+        <v>442</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.08333492894726169</v>
+        <v>0.07402588645314596</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.08333492894726169</v>
+        <v>0.02973490061731673</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.02904562736847527</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.2576247897817361</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.2593252365148109</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-771</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.3470277377742617</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.05010604933980681</v>
+        <v>-0.08955652546533679</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0.2129780609267543</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-661</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -5845,34 +5854,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43578</v>
+        <v>40592</v>
       </c>
       <c r="M8" t="n">
-        <v>145</v>
+        <v>848</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4640066041578759</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.465234323249737</v>
       </c>
       <c r="P8" t="n">
-        <v>142</v>
+        <v>846</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05741014267468564</v>
+        <v>0.2041127217184315</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0368691752791789</v>
+        <v>0.1132470213716198</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5882,52 +5891,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4640066041578759</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.465234323249737</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>-367</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.8656946293691801</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.003640295671724025</v>
+        <v>-0.006044404711033735</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.006596246550614526</v>
       </c>
       <c r="AH8" t="n">
-        <v>28</v>
+        <v>-257</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.007115552064425712</v>
+        <v>-0.01699984046916761</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01713227410894169</v>
+        <v>0.001229378895811317</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>-251</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5978,76 +5987,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+        <v>40361</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>40528</v>
+      </c>
       <c r="M9" t="n">
-        <v>353</v>
+        <v>804</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1635746138652395</v>
+        <v>-0.1491889703005721</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1652260547018467</v>
+        <v>-0.1552830514660811</v>
       </c>
       <c r="P9" t="n">
-        <v>351</v>
+        <v>799</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.08333492894726213</v>
+        <v>0.05818322981533047</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.08333492894726213</v>
+        <v>0.03143392662025841</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.02904562736847571</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>688</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1635746138652395</v>
+        <v>-0.1491889703005721</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1652260547018467</v>
+        <v>-0.1552830514660811</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-744</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1955639039378525</v>
+        <v>0.1753491258255986</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.05010604933980726</v>
+        <v>-0.08785749946239511</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-5.551115123125783e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.3214138804079183</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-634</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -6103,34 +6116,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43578</v>
+        <v>41124</v>
       </c>
       <c r="M10" t="n">
-        <v>145</v>
+        <v>1215</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436488</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="P10" t="n">
-        <v>142</v>
+        <v>1213</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.05741014267468564</v>
+        <v>0.2116830145154624</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.0368691752791789</v>
+        <v>0.1405580320867841</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6140,52 +6153,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.163574613865239</v>
+        <v>-0.4703749864436488</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1652260547018463</v>
+        <v>-0.4715881184443683</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>81</v>
+        <v>860</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1955639039378518</v>
+        <v>0.8881283444019241</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.003640295671724025</v>
+        <v>0.02126660600413061</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0</v>
+        <v>0.0002278642648415596</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.007115552064425712</v>
+        <v>0.01031117024599673</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01713227410894169</v>
+        <v>-0.005139003389961649</v>
       </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6488,34 +6501,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6525,22 +6538,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6549,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6597,34 +6610,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M3" t="n">
+        <v>118</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="P3" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.0573135221947752</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.03318305775662167</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M3" t="n">
-        <v>101</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6634,31 +6647,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="AC3" t="n">
-        <v>23</v>
+        <v>-25</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6714,34 +6727,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M4" t="n">
+        <v>134</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P4" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6751,40 +6764,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0008127579317261657</v>
+        <v>-0.00347137060670542</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.01168096208805969</v>
+        <v>0.01780565920008326</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6839,34 +6852,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M5" t="n">
+        <v>118</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1639593569865849</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1652260547018465</v>
+      </c>
+      <c r="P5" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.05731352219477524</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.03318305775662169</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M5" t="n">
-        <v>101</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3019274392708715</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3019274392708715</v>
-      </c>
-      <c r="P5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.131020856211095</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.06077869181898067</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6876,37 +6889,37 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3019274392708715</v>
+        <v>-0.1639593569865849</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3019274392708715</v>
+        <v>-0.1652260547018465</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="AC5" t="n">
-        <v>23</v>
+        <v>-25</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4325158389774151</v>
+        <v>0.1961140984672847</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-8.326672684688674e-17</v>
+        <v>2.081668171172169e-17</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -6968,34 +6981,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43537</v>
+      </c>
+      <c r="M6" t="n">
+        <v>118</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="P6" t="n">
+        <v>115</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.0573135221947752</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03318305775662167</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M6" t="n">
-        <v>101</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7005,31 +7018,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="AC6" t="n">
-        <v>23</v>
+        <v>-25</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>0</v>
@@ -7044,13 +7057,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.0008127579317261657</v>
+        <v>0.00347137060670542</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.01168096208805969</v>
+        <v>-0.01780565920008326</v>
       </c>
       <c r="AL6" t="n">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -7101,80 +7114,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>354</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="P7" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.08321787671987473</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.08321787671987473</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M7" t="n">
-        <v>101</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P7" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.02949225180408288</v>
+      </c>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>23</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0</v>
+        <v>0.05003481896325306</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -7230,34 +7239,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M8" t="n">
+        <v>146</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="P8" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05721595479114579</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.0368181226790492</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M8" t="n">
-        <v>101</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P8" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7267,52 +7276,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AC8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>0.003635064922427531</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.0008127579317261657</v>
+        <v>0.00710643552913295</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01168096208805969</v>
+        <v>-0.01780565920008326</v>
       </c>
       <c r="AL8" t="n">
-        <v>-21</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -7363,80 +7372,76 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>354</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.163959356986585</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1652260547018466</v>
+      </c>
+      <c r="P9" t="n">
+        <v>352</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.08321787671987491</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.08321787671987491</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M9" t="n">
-        <v>101</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P9" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.131020856211095</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06077869181898066</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.02949225180408332</v>
+      </c>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.163959356986585</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018466</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>23</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.1961140984672849</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-9.71445146547012e-17</v>
+        <v>0.05003481896325324</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.551115123125783e-16</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7492,34 +7497,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M10" t="n">
+        <v>146</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1639593569865845</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1652260547018464</v>
+      </c>
+      <c r="P10" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.05721595479114579</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.0368181226790492</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44026</v>
-      </c>
-      <c r="M10" t="n">
-        <v>101</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3019274392708716</v>
-      </c>
-      <c r="P10" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1310208562110952</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06077869181898075</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7529,52 +7534,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1639593569865845</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3019274392708716</v>
+        <v>-0.1652260547018464</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AC10" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4325158389774153</v>
+        <v>0.196114098467284</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0</v>
+        <v>0.003635064922427531</v>
       </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.0008127579317261657</v>
+        <v>0.00710643552913295</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01168096208805969</v>
+        <v>-0.01780565920008326</v>
       </c>
       <c r="AL10" t="n">
-        <v>-21</v>
+        <v>12</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7877,34 +7882,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7914,22 +7919,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7938,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7986,34 +7991,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M3" t="n">
+        <v>101</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P3" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45072</v>
-      </c>
-      <c r="M3" t="n">
-        <v>351</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="P3" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1993947475706169</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1335211970875572</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8023,31 +8028,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="AC3" t="n">
-        <v>-64</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4793846220779194</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8103,34 +8108,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M4" t="n">
-        <v>383</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="P4" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1328475678049171</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09291469197671884</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8140,40 +8145,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-32</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.04060650511083833</v>
+        <v>-0.0008127579317261657</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08576084484098734</v>
+        <v>0.01168096208805969</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8228,73 +8233,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M5" t="n">
+        <v>101</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3019274392708715</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3019274392708715</v>
+      </c>
+      <c r="P5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.131020856211095</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.06077869181898067</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>513</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.01186277237784117</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0007600484582676122</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3019274392708715</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.3019274392708715</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AC5" t="n">
-        <v>-220</v>
+        <v>23</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.4325158389774151</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1335211970875572</v>
+        <v>-8.326672684688674e-17</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.324043264289569</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="AH5" t="n">
-        <v>-156</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8303,12 +8312,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.3582787676295329</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.2634396529978946</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8357,34 +8362,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M6" t="n">
+        <v>101</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M6" t="n">
-        <v>383</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P6" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8394,62 +8399,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="AC6" t="n">
-        <v>-32</v>
+        <v>23</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04060650511083784</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.08576084484098634</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.0008127579317261657</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.01168096208805969</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.3582787676295329</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.0883258250595057</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8494,34 +8495,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M7" t="n">
+        <v>101</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P7" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45456</v>
-      </c>
-      <c r="M7" t="n">
-        <v>614</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="P7" t="n">
-        <v>613</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.2285524441464575</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.2022966073972135</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8531,40 +8532,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AC7" t="n">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4793846220779194</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.06877541030965637</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8623,34 +8624,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M8" t="n">
+        <v>101</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P8" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45327</v>
-      </c>
-      <c r="M8" t="n">
-        <v>524</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.324043264289569</v>
-      </c>
-      <c r="P8" t="n">
-        <v>523</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1997979170146728</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.163393877645268</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8660,52 +8661,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.324043264289569</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="AC8" t="n">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4793846220779194</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.02987268055771083</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.07047918566854916</v>
+        <v>0.0008127579317261657</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.08576084484098734</v>
+        <v>-0.01168096208805969</v>
       </c>
       <c r="AL8" t="n">
-        <v>141</v>
+        <v>-21</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -8756,73 +8757,77 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M9" t="n">
+        <v>101</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.131020856211095</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06077869181898066</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>513</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.01186277237784117</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.0007600484582676122</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>23</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1335211970875572</v>
+        <v>-9.71445146547012e-17</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.324043264289569</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-156</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8881,34 +8886,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="M10" t="n">
+        <v>101</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3019274392708716</v>
+      </c>
+      <c r="P10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1310208562110952</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.06077869181898075</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M10" t="n">
-        <v>383</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P10" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1328475678049178</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09291469197671932</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8918,52 +8923,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.3019274392708716</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="AC10" t="n">
-        <v>-32</v>
+        <v>23</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4325158389774153</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.04060650511083784</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.08576084484098634</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>4.85722573273506e-16</v>
+        <v>0.0008127579317261657</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>-0.01168096208805969</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -9266,34 +9271,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451827</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9303,22 +9308,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9327,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088539</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9375,34 +9380,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45072</v>
+      </c>
+      <c r="M3" t="n">
+        <v>351</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="P3" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1993947475706169</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1335211970875572</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45861</v>
-      </c>
-      <c r="M3" t="n">
-        <v>106</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1878863304044792</v>
-      </c>
-      <c r="P3" t="n">
-        <v>105</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.08429914349524448</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05905909723216233</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9412,31 +9417,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1878863304044792</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>-64</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2313547197131374</v>
+        <v>0.4793846220779194</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9492,34 +9497,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M4" t="n">
+        <v>383</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="P4" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1328475678049171</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09291469197671884</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M4" t="n">
-        <v>108</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="P4" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06372707386676911</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.04506184607636846</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9529,40 +9534,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC4" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01399725115579387</v>
+        <v>-0.04060650511083833</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03227471079173017</v>
+        <v>0.08576084484098734</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9617,30 +9622,30 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.01186277237784117</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0007600484582676122</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -9653,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -9668,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
@@ -9677,13 +9682,13 @@
         <v>0</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.05905909723216233</v>
+        <v>-0.1335211970875572</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1878863304044792</v>
+        <v>0.324043264289569</v>
       </c>
       <c r="AH5" t="n">
-        <v>-72</v>
+        <v>-156</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9693,10 +9698,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.03585765398568408</v>
+        <v>0.3582787676295329</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.02974365309812033</v>
+        <v>-0.2634396529978946</v>
       </c>
     </row>
     <row r="6">
@@ -9746,34 +9751,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M6" t="n">
+        <v>383</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P6" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M6" t="n">
-        <v>108</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P6" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9783,49 +9788,49 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC6" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01399725115579394</v>
+        <v>-0.04060650511083784</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03227471079173028</v>
+        <v>0.08576084484098634</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -9834,10 +9839,10 @@
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.03585765398568408</v>
+        <v>0.3582787676295329</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.02898025511974711</v>
+        <v>-0.0883258250595057</v>
       </c>
     </row>
     <row r="7">
@@ -9883,73 +9888,77 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45456</v>
+      </c>
+      <c r="M7" t="n">
+        <v>614</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="P7" t="n">
+        <v>613</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.2285524441464575</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.2022966073972135</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>88</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>199</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.4793846220779194</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.05905909723216233</v>
+        <v>0.06877541030965637</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1878863304044792</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-72</v>
+        <v>263</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9958,12 +9967,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.02974365309812033</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10012,34 +10017,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45327</v>
+      </c>
+      <c r="M8" t="n">
+        <v>524</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.324043264289569</v>
+      </c>
+      <c r="P8" t="n">
+        <v>523</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1997979170146728</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.163393877645268</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M8" t="n">
-        <v>108</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P8" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10049,62 +10054,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.324043264289569</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>74</v>
+        <v>329</v>
       </c>
       <c r="AC8" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.4793846220779194</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01399725115579394</v>
+        <v>0.02987268055771083</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03227471079173028</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>0.07047918566854916</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-0.08576084484098734</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>0.02898025511974711</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10149,30 +10150,30 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.01186277237784117</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.0007600484582676122</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -10185,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>0</v>
@@ -10200,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
@@ -10209,13 +10210,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.05905909723216233</v>
+        <v>-0.1335211970875572</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1878863304044792</v>
+        <v>0.324043264289569</v>
       </c>
       <c r="AH9" t="n">
-        <v>-72</v>
+        <v>-156</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10224,12 +10225,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.02974365309812033</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10278,34 +10275,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M10" t="n">
+        <v>383</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P10" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1328475678049178</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09291469197671932</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M10" t="n">
-        <v>108</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1556116196127489</v>
-      </c>
-      <c r="P10" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.06372707386676901</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04506184607636839</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10315,49 +10312,49 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1556116196127489</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1842891532228128</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.01399725115579394</v>
+        <v>-0.04060650511083784</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.03227471079173028</v>
+        <v>0.08576084484098634</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-6.938893903907228e-17</v>
+        <v>4.85722573273506e-16</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -10365,12 +10362,8 @@
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.03585765398568408</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0.02898025511974711</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10383,7 +10376,1408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451827</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45861</v>
+      </c>
+      <c r="M3" t="n">
+        <v>106</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="P3" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.08429914349524448</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05905909723216233</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1878863304044792</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2313547197131374</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M4" t="n">
+        <v>108</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="P4" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06372707386676911</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04506184607636846</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.184289153222813</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.01399725115579387</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.03227471079173017</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.05905909723216233</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.1878863304044792</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M6" t="n">
+        <v>108</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P6" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.01399725115579394</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.03227471079173028</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>89</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.05905909723216233</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.1878863304044792</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M8" t="n">
+        <v>108</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P8" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.01399725115579394</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.03227471079173028</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>89</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>1</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.05905909723216233</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.1878863304044792</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.02974365309812033</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M10" t="n">
+        <v>108</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="P10" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.06372707386676901</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.04506184607636839</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1556116196127489</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.1842891532228128</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>-0.01399725115579394</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.03227471079173028</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>-6.938893903907228e-17</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="n">
+        <v>0.03585765398568408</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.02898025511974711</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10489,12 +11883,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -10503,10 +11893,10 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10537,10 +11927,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -10550,7 +11940,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -10583,8 +11973,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -10593,10 +11987,10 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10669,24 +12063,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10717,21 +12107,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10748,30 +12140,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -10801,15 +12195,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -10818,10 +12208,10 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10848,7 +12238,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -10857,16 +12247,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10893,11 +12281,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -10906,10 +12298,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10936,7 +12328,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -10948,13 +12340,13 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -10981,22 +12373,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -11016,37 +12406,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11063,37 +12451,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11120,25 +12506,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11165,11 +12553,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -11178,10 +12570,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11208,14 +12600,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -11225,7 +12617,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -11255,30 +12647,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
